--- a/data/trans_dic/P57B3_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57B3_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,95</t>
+          <t>1,11; 6,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,69</t>
+          <t>4,73; 13,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,25</t>
+          <t>3,25; 7,86</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 10,56</t>
+          <t>5,17; 11,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,21</t>
+          <t>7,18; 12,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,24</t>
+          <t>6,78; 10,78</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 13,92</t>
+          <t>9,58; 15,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,0</t>
+          <t>5,96; 9,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 10,77</t>
+          <t>8,32; 11,82</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 73,34</t>
+          <t>9,76; 14,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,46</t>
+          <t>8,04; 11,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 57,36</t>
+          <t>9,4; 12,41</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,96; 19,69</t>
+          <t>14,11; 19,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 17,07</t>
+          <t>12,81; 17,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,02; 17,67</t>
+          <t>14,32; 17,91</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,02; 15,43</t>
+          <t>9,59; 15,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 20,61</t>
+          <t>17,17; 22,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,79; 16,96</t>
+          <t>14,47; 18,19</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,64; 22,27</t>
+          <t>15,15; 22,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,07; 31,04</t>
+          <t>25,22; 31,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,14; 26,91</t>
+          <t>22,04; 26,71</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,97; 37,04</t>
+          <t>10,71; 13,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,8; 13,21</t>
+          <t>12,62; 14,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,54; 26,32</t>
+          <t>12,02; 13,44</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>28493</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>39810</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3216; 23815</t>
+          <t>4521; 25518</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13070; 39744</t>
+          <t>17133; 47173</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19265; 51721</t>
+          <t>25003; 60515</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>28230</t>
+          <t>36690</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66009</t>
+          <t>83973</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18707; 44737</t>
+          <t>24662; 52593</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23585; 52248</t>
+          <t>35960; 64915</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48561; 86426</t>
+          <t>66265; 105417</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58822</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>47683</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>121948</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44059; 74522</t>
+          <t>59339; 93092</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29927; 48683</t>
+          <t>36998; 61115</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81461; 115886</t>
+          <t>103199; 146574</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>320013</t>
+          <t>83977</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>61051</t>
+          <t>72769</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381065</t>
+          <t>156746</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95773; 651082</t>
+          <t>68412; 103382</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48509; 74475</t>
+          <t>59176; 86179</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151201; 917479</t>
+          <t>135039; 178311</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>93402</t>
+          <t>103311</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>91395</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174566</t>
+          <t>194706</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>78362; 110483</t>
+          <t>85992; 121118</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69767; 93343</t>
+          <t>77797; 105837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155349; 195747</t>
+          <t>174266; 217913</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>50117</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>79196</t>
+          <t>87670</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125463</t>
+          <t>137787</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36890; 56824</t>
+          <t>39025; 61212</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35793; 125401</t>
+          <t>75419; 98930</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66290; 165595</t>
+          <t>122448; 153947</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>53223</t>
+          <t>57362</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>118815</t>
+          <t>129515</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>172038</t>
+          <t>186877</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44082; 62780</t>
+          <t>46864; 68286</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>106304; 131610</t>
+          <t>116695; 144847</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156265; 189921</t>
+          <t>170143; 206191</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>609334</t>
+          <t>417039</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>504807</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1049824</t>
+          <t>921846</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>379463; 1280857</t>
+          <t>378278; 460031</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>358236; 482937</t>
+          <t>470570; 542857</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>820712; 1872786</t>
+          <t>872490; 975451</t>
         </is>
       </c>
     </row>
